--- a/引脚定义.xlsx
+++ b/引脚定义.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\研电赛\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Keil5\project\GD32A7xx_B__FreeRTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3D78DB-944F-4EAB-8780-1C6477608D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6C67DD-EBED-480B-9D33-32A85356EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,12 +242,6 @@
     <t>故障电流监测</t>
   </si>
   <si>
-    <t>加热片 1 电流监测</t>
-  </si>
-  <si>
-    <t>加热片 1 电流 ADC 采样</t>
-  </si>
-  <si>
     <t>制冷片 1 电流监测</t>
   </si>
   <si>
@@ -353,12 +347,80 @@
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MQ9 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电流监测</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MQ9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>电流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ADC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>采样</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -371,12 +433,14 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -384,12 +448,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -456,6 +522,12 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -609,7 +681,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -650,6 +722,45 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -665,12 +776,6 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -683,37 +788,7 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1182,439 +1257,439 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="26">
+      <c r="D2" s="17">
         <v>83</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="17" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="27" t="s">
-        <v>94</v>
+      <c r="B3" s="18" t="s">
+        <v>92</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="19">
         <v>29</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30"/>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="17">
         <v>89</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="19">
         <v>90</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="19" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="22"/>
+      <c r="B6" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="17">
         <v>91</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="31"/>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="23"/>
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="19">
         <v>92</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="28" t="s">
+      <c r="F7" s="19" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="17">
         <v>30</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34"/>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="25"/>
+      <c r="B9" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="19">
         <v>31</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="19" t="s">
         <v>49</v>
       </c>
       <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34"/>
-      <c r="B10" s="26" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="17">
         <v>35</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="17" t="s">
         <v>52</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35"/>
-      <c r="B11" s="28" t="s">
+      <c r="A11" s="26"/>
+      <c r="B11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="19">
         <v>36</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="19" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="17">
         <v>40</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="17" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="28" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="28" t="s">
+      <c r="C13" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="19">
         <v>41</v>
       </c>
-      <c r="E13" s="28" t="s">
+      <c r="E13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="17">
         <v>42</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="17" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="28" t="s">
+      <c r="A15" s="29"/>
+      <c r="B15" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="19">
         <v>76</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="F15" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="17">
+        <v>100</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="31"/>
+      <c r="B17" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="26" t="s">
-        <v>8</v>
+      <c r="C17" s="19" t="s">
+        <v>6</v>
       </c>
-      <c r="D16" s="26">
-        <v>100</v>
+      <c r="D17" s="19">
+        <v>99</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>9</v>
+      <c r="E17" s="19" t="s">
+        <v>7</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F17" s="19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="28" t="s">
+    <row r="18" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="28">
-        <v>99</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="28" t="s">
+      <c r="C18" s="17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="D18" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="17">
+        <v>1</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="19">
         <v>3</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>73</v>
+      <c r="E21" s="19" t="s">
+        <v>14</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>74</v>
+      <c r="F21" s="19" t="s">
+        <v>80</v>
       </c>
-      <c r="D18" s="26" t="s">
-        <v>75</v>
+    </row>
+    <row r="22" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
+        <v>82</v>
       </c>
-      <c r="E18" s="26" t="s">
-        <v>4</v>
+      <c r="B22" s="17" t="s">
+        <v>18</v>
       </c>
-      <c r="F18" s="26" t="s">
-        <v>76</v>
+      <c r="C22" s="17" t="s">
+        <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>5</v>
+      <c r="D22" s="17">
+        <v>43</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>77</v>
+      <c r="E22" s="17" t="s">
+        <v>16</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="F22" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="35"/>
+      <c r="B23" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="19">
+        <v>44</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="26">
-        <v>1</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22"/>
-      <c r="B21" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="28">
-        <v>3</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="28" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="D22" s="26">
-        <v>43</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="28">
-        <v>44</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B24" s="26" t="s">
+      <c r="F24" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -29766,12 +29841,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A22:A23"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/引脚定义.xlsx
+++ b/引脚定义.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Keil5\project\GD32A7xx_B__FreeRTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6C67DD-EBED-480B-9D33-32A85356EFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9BE457-7F40-41F8-9E50-17122DED745C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="96">
   <si>
     <t>功能类别</t>
   </si>
@@ -415,12 +415,16 @@
     </r>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
+  <si>
+    <t>Next Team - Intelligent Thermal Management System for Automotive Power Batteries Based on GD32A712 Chip</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -529,8 +533,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,8 +626,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -676,12 +693,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -743,6 +769,15 @@
     <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -782,14 +817,11 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1223,7 +1255,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1038"/>
+  <dimension ref="A1:Z1039"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.28515625" style="1" customWidth="1"/>
@@ -1236,472 +1268,479 @@
     <col min="8" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="12" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:7" s="12" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+    <row r="3" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B3" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D3" s="17">
         <v>83</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+    <row r="4" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B4" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D4" s="19">
         <v>29</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="17" t="s">
+    <row r="5" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D5" s="17">
         <v>89</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22"/>
-      <c r="B5" s="19" t="s">
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C6" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D6" s="19">
         <v>90</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="17" t="s">
+    <row r="7" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25"/>
+      <c r="B7" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C7" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D7" s="17">
         <v>91</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F7" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="19" t="s">
+    <row r="8" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D8" s="19">
         <v>92</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F8" s="19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24" t="s">
+    <row r="9" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D9" s="17">
         <v>30</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F9" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="19" t="s">
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28"/>
+      <c r="B10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D10" s="19">
         <v>31</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F10" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="17" t="s">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D11" s="17">
         <v>35</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F11" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="19" t="s">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29"/>
+      <c r="B12" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D12" s="19">
         <v>36</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F12" s="19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+    <row r="13" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B13" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D13" s="17">
         <v>40</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F13" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="19" t="s">
+    <row r="14" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="31"/>
+      <c r="B14" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C14" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D14" s="19">
         <v>41</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F14" s="19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
-      <c r="B14" s="17" t="s">
+    <row r="15" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="31"/>
+      <c r="B15" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C15" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D15" s="17">
         <v>42</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="29"/>
-      <c r="B15" s="19" t="s">
+    <row r="16" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
+      <c r="B16" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C16" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D16" s="19">
         <v>76</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E16" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F16" s="19" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+    <row r="17" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B17" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C17" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D17" s="17">
         <v>100</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E17" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F17" s="21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
-      <c r="B17" s="19" t="s">
+    <row r="18" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="34"/>
+      <c r="B18" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C18" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D18" s="19">
         <v>99</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E18" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F18" s="19" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="19" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B19" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C19" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E19" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F19" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="20" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B20" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D20" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E20" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F20" s="19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32" t="s">
+    <row r="21" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B21" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C21" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D21" s="17">
         <v>1</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F21" s="17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="19" t="s">
+    <row r="22" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="36"/>
+      <c r="B22" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C22" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D22" s="19">
         <v>3</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E22" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F22" s="19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34" t="s">
+    <row r="23" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B23" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C23" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D23" s="17">
         <v>43</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E23" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F23" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="19" t="s">
+    <row r="24" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+      <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C24" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D24" s="19">
         <v>44</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E24" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F24" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="25" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C25" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D25" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E25" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F25" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
@@ -1724,33 +1763,8 @@
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
     </row>
-    <row r="34" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
+    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2"/>
     </row>
     <row r="35" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
@@ -1836,7 +1850,7 @@
       <c r="Y37" s="6"/>
       <c r="Z37" s="6"/>
     </row>
-    <row r="38" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -1867,51 +1881,56 @@
     <row r="39" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="N39" s="7"/>
-      <c r="O39" s="7"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="7"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="T39" s="7"/>
-      <c r="U39" s="7"/>
-    </row>
-    <row r="40" spans="1:26" ht="44.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="9"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-    </row>
-    <row r="41" spans="1:26" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6"/>
+    </row>
+    <row r="40" spans="1:26" s="1" customFormat="1" ht="48.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+    </row>
+    <row r="41" spans="1:26" ht="44.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
       <c r="B41" s="8"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
@@ -1933,7 +1952,7 @@
       <c r="T41" s="10"/>
       <c r="U41" s="10"/>
     </row>
-    <row r="42" spans="1:26" ht="98.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:26" ht="69" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="10"/>
@@ -1956,7 +1975,7 @@
       <c r="T42" s="10"/>
       <c r="U42" s="10"/>
     </row>
-    <row r="43" spans="1:26" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:26" ht="98.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="10"/>
@@ -1979,13 +1998,13 @@
       <c r="T43" s="10"/>
       <c r="U43" s="10"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="10"/>
+    <row r="44" spans="1:26" ht="75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
-      <c r="F44" s="11"/>
+      <c r="F44" s="10"/>
       <c r="G44" s="10"/>
       <c r="H44" s="10"/>
       <c r="I44" s="10"/>
@@ -2001,13 +2020,8 @@
       <c r="S44" s="10"/>
       <c r="T44" s="10"/>
       <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-      <c r="Y44" s="10"/>
-      <c r="Z44" s="10"/>
-    </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A45" s="7"/>
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
@@ -29839,14 +29853,43 @@
       <c r="Y1038" s="10"/>
       <c r="Z1038" s="10"/>
     </row>
+    <row r="1039" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1039" s="7"/>
+      <c r="B1039" s="10"/>
+      <c r="C1039" s="10"/>
+      <c r="D1039" s="10"/>
+      <c r="E1039" s="10"/>
+      <c r="F1039" s="11"/>
+      <c r="G1039" s="10"/>
+      <c r="H1039" s="10"/>
+      <c r="I1039" s="10"/>
+      <c r="J1039" s="10"/>
+      <c r="K1039" s="10"/>
+      <c r="L1039" s="10"/>
+      <c r="M1039" s="10"/>
+      <c r="N1039" s="10"/>
+      <c r="O1039" s="10"/>
+      <c r="P1039" s="10"/>
+      <c r="Q1039" s="10"/>
+      <c r="R1039" s="10"/>
+      <c r="S1039" s="10"/>
+      <c r="T1039" s="10"/>
+      <c r="U1039" s="10"/>
+      <c r="V1039" s="10"/>
+      <c r="W1039" s="10"/>
+      <c r="X1039" s="10"/>
+      <c r="Y1039" s="10"/>
+      <c r="Z1039" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A20:A21"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A21:A22"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/引脚定义.xlsx
+++ b/引脚定义.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Keil5\project\GD32A7xx_B__FreeRTOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9BE457-7F40-41F8-9E50-17122DED745C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F0FB3D-DCBC-4A04-90B1-8D632CDBE6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GD32引脚分配汇总与建议" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>GPIO_Output</t>
   </si>
   <si>
-    <t>PF0</t>
-  </si>
-  <si>
     <t>报警蜂鸣器</t>
   </si>
   <si>
@@ -99,9 +96,6 @@
   </si>
   <si>
     <t>PF10</t>
-  </si>
-  <si>
-    <t>PE10</t>
   </si>
   <si>
     <t>PG0</t>
@@ -140,25 +134,16 @@
     <t>正常运行（绿灯）</t>
   </si>
   <si>
-    <t>PE11</t>
-  </si>
-  <si>
     <t>系统正常运行指示</t>
   </si>
   <si>
     <t>高温预警（黄灯）</t>
   </si>
   <si>
-    <t>PE12</t>
-  </si>
-  <si>
     <t>系统高温预警指示</t>
   </si>
   <si>
     <t>危险告警（红灯）</t>
-  </si>
-  <si>
-    <t>PE13</t>
   </si>
   <si>
     <t>危险紧急/逃生告警指示</t>
@@ -417,6 +402,26 @@
   </si>
   <si>
     <t>Next Team - Intelligent Thermal Management System for Automotive Power Batteries Based on GD32A712 Chip</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG2</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG3</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG4</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PG5</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>PF0</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -772,6 +777,12 @@
     <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -816,12 +827,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1269,21 +1274,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37" t="s">
-        <v>95</v>
+      <c r="A1" s="22" t="s">
+        <v>90</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
     </row>
     <row r="2" spans="1:7" s="12" customFormat="1" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="13" t="s">
         <v>1</v>
@@ -1292,21 +1297,21 @@
         <v>2</v>
       </c>
       <c r="E2" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>28</v>
-      </c>
       <c r="C3" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="17">
         <v>83</v>
@@ -1315,18 +1320,18 @@
         <v>16</v>
       </c>
       <c r="F3" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>31</v>
-      </c>
       <c r="B4" s="18" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="D4" s="19">
         <v>29</v>
@@ -1335,90 +1340,90 @@
         <v>16</v>
       </c>
       <c r="F4" s="19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="27"/>
+      <c r="B5" s="17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="17" t="s">
-        <v>32</v>
-      </c>
       <c r="C5" s="17" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="D5" s="17">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D6" s="19">
-        <v>90</v>
+        <v>134</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D7" s="17">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="26"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="19" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="D8" s="19">
-        <v>92</v>
+        <v>136</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>43</v>
+      <c r="A9" s="29" t="s">
+        <v>38</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D9" s="17">
         <v>30</v>
@@ -1427,16 +1432,16 @@
         <v>16</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D10" s="19">
         <v>31</v>
@@ -1445,17 +1450,17 @@
         <v>16</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="17" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D11" s="17">
         <v>35</v>
@@ -1464,17 +1469,17 @@
         <v>16</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
+      <c r="A12" s="31"/>
       <c r="B12" s="19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12" s="19">
         <v>36</v>
@@ -1483,15 +1488,15 @@
         <v>16</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
-        <v>56</v>
+      <c r="A13" s="32" t="s">
+        <v>51</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>15</v>
@@ -1503,16 +1508,16 @@
         <v>16</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
+      <c r="A14" s="33"/>
       <c r="B14" s="19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D14" s="19">
         <v>41</v>
@@ -1521,16 +1526,16 @@
         <v>16</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
+      <c r="A15" s="33"/>
       <c r="B15" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D15" s="17">
         <v>42</v>
@@ -1539,16 +1544,16 @@
         <v>16</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="19" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D16" s="19">
         <v>76</v>
@@ -1557,15 +1562,15 @@
         <v>16</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
-        <v>68</v>
+      <c r="A17" s="35" t="s">
+        <v>63</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>8</v>
@@ -1577,13 +1582,13 @@
         <v>9</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>6</v>
@@ -1595,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1603,19 +1608,19 @@
         <v>3</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>4</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1623,27 +1628,27 @@
         <v>5</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>11</v>
@@ -1655,13 +1660,13 @@
         <v>12</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="36"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>13</v>
@@ -1673,18 +1678,18 @@
         <v>14</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>82</v>
+      <c r="A23" s="24" t="s">
+        <v>77</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" s="17">
         <v>43</v>
@@ -1693,16 +1698,16 @@
         <v>16</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
+      <c r="A24" s="25"/>
       <c r="B24" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D24" s="19">
         <v>44</v>
@@ -1711,27 +1716,27 @@
         <v>16</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="D25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="17" t="s">
-        <v>91</v>
-      </c>
       <c r="F25" s="17" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
